--- a/MathTechPy/data/ExamA02Score.xlsx
+++ b/MathTechPy/data/ExamA02Score.xlsx
@@ -928,7 +928,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>清濑灰二</t>
+          <t>日向翔阳</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1235,7 +1235,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>藏原走</t>
+          <t>影山飞雄</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1542,7 +1542,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>城太郎</t>
+          <t>黑子哲也</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1849,7 +1849,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>城次郎</t>
+          <t>越前龙马</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2156,7 +2156,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>穆萨</t>
+          <t>洁世一</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -16799,7 +16799,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>清濑灰二</t>
+          <t>日向翔阳</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -17106,7 +17106,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>藏原走</t>
+          <t>影山飞雄</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -17413,7 +17413,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>城太郎</t>
+          <t>黑子哲也</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -17720,7 +17720,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>城次郎</t>
+          <t>越前龙马</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -18027,7 +18027,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>穆萨</t>
+          <t>洁世一</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/MathTechPy/data/ExamA02Score.xlsx
+++ b/MathTechPy/data/ExamA02Score.xlsx
@@ -16821,7 +16821,7 @@
         <v>23.1</v>
       </c>
       <c r="H2" t="n">
-        <v>18.7</v>
+        <v>59.9</v>
       </c>
       <c r="I2" t="n">
         <v>25</v>
@@ -16833,7 +16833,7 @@
         <v>30.7</v>
       </c>
       <c r="L2" t="n">
-        <v>22.9</v>
+        <v>70.7</v>
       </c>
       <c r="M2" t="n">
         <v>30.4</v>
@@ -16842,7 +16842,7 @@
         <v>30.5</v>
       </c>
       <c r="O2" t="n">
-        <v>11.7</v>
+        <v>49.5</v>
       </c>
       <c r="P2" t="n">
         <v>19.8</v>
@@ -16866,7 +16866,7 @@
         <v>33.1</v>
       </c>
       <c r="W2" t="n">
-        <v>21.4</v>
+        <v>59.4</v>
       </c>
       <c r="X2" t="n">
         <v>31.4</v>
@@ -16896,7 +16896,7 @@
         <v>28.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>55.2</v>
       </c>
       <c r="AH2" t="n">
         <v>29.7</v>
@@ -17049,7 +17049,7 @@
         <v>29.5</v>
       </c>
       <c r="CF2" t="n">
-        <v>17.1</v>
+        <v>52.6</v>
       </c>
       <c r="CG2" t="n">
         <v>25.8</v>
@@ -17423,7 +17423,7 @@
         <v>30.8</v>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>39.1</v>
@@ -17435,7 +17435,7 @@
         <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>97.5</v>
       </c>
       <c r="I4" t="n">
         <v>34.5</v>
@@ -17447,19 +17447,19 @@
         <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>32.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>28.3</v>
+        <v>72.5</v>
       </c>
       <c r="N4" t="n">
-        <v>30.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>27.9</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>33.5</v>
+        <v>91.3</v>
       </c>
       <c r="Q4" t="n">
         <v>29.2</v>
@@ -17489,19 +17489,19 @@
         <v>32.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>27.6</v>
+        <v>76.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>25.5</v>
+        <v>69.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.2</v>
+        <v>61.1</v>
       </c>
       <c r="AC4" t="n">
         <v>30.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>27.5</v>
+        <v>90</v>
       </c>
       <c r="AE4" t="n">
         <v>26.5</v>
@@ -17510,13 +17510,13 @@
         <v>31.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>21.9</v>
+        <v>61.6</v>
       </c>
       <c r="AH4" t="n">
         <v>29.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>20</v>
+        <v>64.2</v>
       </c>
       <c r="AJ4" t="n">
         <v>27.8</v>
@@ -17537,7 +17537,7 @@
         <v>30.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>25</v>
+        <v>80.7</v>
       </c>
       <c r="AQ4" t="n">
         <v>35</v>
@@ -17555,7 +17555,7 @@
         <v>30.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>27.7</v>
+        <v>75.3</v>
       </c>
       <c r="AW4" t="n">
         <v>32.2</v>
@@ -17582,10 +17582,10 @@
         <v>29.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>23.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>32.9</v>
+        <v>93.8</v>
       </c>
       <c r="BG4" t="n">
         <v>43</v>
@@ -17594,16 +17594,16 @@
         <v>31.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>23.8</v>
+        <v>84.3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>22.3</v>
+        <v>51.5</v>
       </c>
       <c r="BK4" t="n">
         <v>38.3</v>
       </c>
       <c r="BL4" t="n">
-        <v>23.6</v>
+        <v>86</v>
       </c>
       <c r="BM4" t="n">
         <v>30.2</v>
@@ -17615,10 +17615,10 @@
         <v>36.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>24.3</v>
+        <v>64.7</v>
       </c>
       <c r="BQ4" t="n">
-        <v>30.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>29.8</v>
@@ -17627,7 +17627,7 @@
         <v>24.9</v>
       </c>
       <c r="BT4" t="n">
-        <v>30.2</v>
+        <v>85.8</v>
       </c>
       <c r="BU4" t="n">
         <v>32.6</v>
@@ -17645,7 +17645,7 @@
         <v>31.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>27.5</v>
+        <v>86.2</v>
       </c>
       <c r="CA4" t="n">
         <v>31.3</v>
@@ -17663,7 +17663,7 @@
         <v>34.8</v>
       </c>
       <c r="CF4" t="n">
-        <v>31.6</v>
+        <v>88.8</v>
       </c>
       <c r="CG4" t="n">
         <v>43.3</v>
@@ -17684,7 +17684,7 @@
         <v>36.3</v>
       </c>
       <c r="CM4" t="n">
-        <v>26</v>
+        <v>78.7</v>
       </c>
       <c r="CN4" t="n">
         <v>36.4</v>
@@ -17702,7 +17702,7 @@
         <v>33.2</v>
       </c>
       <c r="CS4" t="n">
-        <v>25.9</v>
+        <v>79.3</v>
       </c>
       <c r="CT4" t="n">
         <v>35.5</v>
@@ -17711,7 +17711,7 @@
         <v>28.6</v>
       </c>
       <c r="CV4" t="n">
-        <v>19.9</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="CW4" t="n">
         <v>32.9</v>
@@ -18058,7 +18058,7 @@
         <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>19.1</v>
+        <v>45.1</v>
       </c>
       <c r="L6" t="n">
         <v>36.1</v>
@@ -18160,7 +18160,7 @@
         <v>26.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>19.4</v>
+        <v>52.2</v>
       </c>
       <c r="AT6" t="n">
         <v>27.6</v>
@@ -18325,7 +18325,7 @@
         <v>26.7</v>
       </c>
       <c r="CV6" t="n">
-        <v>18.7</v>
+        <v>61.6</v>
       </c>
       <c r="CW6" t="n">
         <v>27</v>
@@ -18651,7 +18651,7 @@
         <v>23.5</v>
       </c>
       <c r="D8" t="n">
-        <v>19.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>29.5</v>
@@ -18669,22 +18669,22 @@
         <v>29.1</v>
       </c>
       <c r="J8" t="n">
-        <v>18.7</v>
+        <v>61.6</v>
       </c>
       <c r="K8" t="n">
-        <v>22.5</v>
+        <v>62.7</v>
       </c>
       <c r="L8" t="n">
         <v>28.5</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>17.4</v>
+        <v>61</v>
       </c>
       <c r="O8" t="n">
-        <v>22.1</v>
+        <v>76.7</v>
       </c>
       <c r="P8" t="n">
         <v>26.1</v>
@@ -18693,22 +18693,22 @@
         <v>24.5</v>
       </c>
       <c r="R8" t="n">
-        <v>22.5</v>
+        <v>60.6</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>14.3</v>
+        <v>56.2</v>
       </c>
       <c r="U8" t="n">
-        <v>24</v>
+        <v>73.5</v>
       </c>
       <c r="V8" t="n">
         <v>26.2</v>
       </c>
       <c r="W8" t="n">
-        <v>20.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>20.8</v>
@@ -18717,7 +18717,7 @@
         <v>24.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.9</v>
+        <v>60.9</v>
       </c>
       <c r="AA8" t="n">
         <v>25.3</v>
@@ -18732,25 +18732,25 @@
         <v>21.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>21.8</v>
+        <v>63.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.4</v>
+        <v>63.2</v>
       </c>
       <c r="AG8" t="n">
         <v>27.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>21.2</v>
+        <v>75.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>21.7</v>
+        <v>54.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>29.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>21.2</v>
+        <v>64.3</v>
       </c>
       <c r="AL8" t="n">
         <v>24.6</v>
@@ -18759,10 +18759,10 @@
         <v>29.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.6</v>
+        <v>54.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>24.5</v>
+        <v>72.5</v>
       </c>
       <c r="AP8" t="n">
         <v>36.3</v>
@@ -18780,10 +18780,10 @@
         <v>32.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>17.9</v>
+        <v>80.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>66.7</v>
       </c>
       <c r="AW8" t="n">
         <v>27.7</v>
@@ -18792,13 +18792,13 @@
         <v>23.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>23.7</v>
+        <v>60.7</v>
       </c>
       <c r="AZ8" t="n">
         <v>21.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>22.2</v>
+        <v>60.3</v>
       </c>
       <c r="BB8" t="n">
         <v>29.1</v>
@@ -18822,43 +18822,43 @@
         <v>29.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>23.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="BJ8" t="n">
-        <v>16.9</v>
+        <v>55.8</v>
       </c>
       <c r="BK8" t="n">
-        <v>24.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="BL8" t="n">
-        <v>22.6</v>
+        <v>59.5</v>
       </c>
       <c r="BM8" t="n">
         <v>23.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>17.8</v>
+        <v>64.7</v>
       </c>
       <c r="BO8" t="n">
         <v>32.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>22.2</v>
+        <v>66</v>
       </c>
       <c r="BQ8" t="n">
         <v>25.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>17.3</v>
+        <v>68.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>16.4</v>
+        <v>60.1</v>
       </c>
       <c r="BT8" t="n">
         <v>22.1</v>
       </c>
       <c r="BU8" t="n">
-        <v>24.3</v>
+        <v>71.2</v>
       </c>
       <c r="BV8" t="n">
         <v>21.7</v>
@@ -18867,13 +18867,13 @@
         <v>34.1</v>
       </c>
       <c r="BX8" t="n">
-        <v>23.2</v>
+        <v>63.3</v>
       </c>
       <c r="BY8" t="n">
-        <v>21.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="BZ8" t="n">
-        <v>20.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="CA8" t="n">
         <v>26.5</v>
@@ -18891,13 +18891,13 @@
         <v>29.1</v>
       </c>
       <c r="CF8" t="n">
-        <v>20.6</v>
+        <v>74.2</v>
       </c>
       <c r="CG8" t="n">
         <v>28.4</v>
       </c>
       <c r="CH8" t="n">
-        <v>9.699999999999999</v>
+        <v>64</v>
       </c>
       <c r="CI8" t="n">
         <v>26.6</v>
@@ -18912,22 +18912,22 @@
         <v>30.6</v>
       </c>
       <c r="CM8" t="n">
-        <v>14.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="CN8" t="n">
-        <v>20.4</v>
+        <v>60.1</v>
       </c>
       <c r="CO8" t="n">
-        <v>21.8</v>
+        <v>62.4</v>
       </c>
       <c r="CP8" t="n">
         <v>27.5</v>
       </c>
       <c r="CQ8" t="n">
-        <v>21.9</v>
+        <v>54</v>
       </c>
       <c r="CR8" t="n">
-        <v>21.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="CS8" t="n">
         <v>24.9</v>
@@ -19584,127 +19584,127 @@
         <v>19.3</v>
       </c>
       <c r="H11" t="n">
-        <v>15.8</v>
+        <v>56.3</v>
       </c>
       <c r="I11" t="n">
-        <v>17.2</v>
+        <v>67.2</v>
       </c>
       <c r="J11" t="n">
-        <v>18.5</v>
+        <v>62</v>
       </c>
       <c r="K11" t="n">
-        <v>12.5</v>
+        <v>45.2</v>
       </c>
       <c r="L11" t="n">
-        <v>14.9</v>
+        <v>67.8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.3</v>
+        <v>61.1</v>
       </c>
       <c r="N11" t="n">
-        <v>12.2</v>
+        <v>51.2</v>
       </c>
       <c r="O11" t="n">
         <v>19.5</v>
       </c>
       <c r="P11" t="n">
-        <v>14.2</v>
+        <v>57.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.7</v>
+        <v>61.8</v>
       </c>
       <c r="R11" t="n">
-        <v>16.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>12.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>13.5</v>
       </c>
       <c r="U11" t="n">
-        <v>12.4</v>
+        <v>84.8</v>
       </c>
       <c r="V11" t="n">
-        <v>14.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>11.7</v>
+        <v>70.3</v>
       </c>
       <c r="X11" t="n">
-        <v>12.6</v>
+        <v>54.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.9</v>
+        <v>52</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>56.5</v>
       </c>
       <c r="AA11" t="n">
         <v>25.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>24.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.4</v>
+        <v>66.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>70.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AF11" t="n">
-        <v>18.4</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>19.6</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>15.5</v>
+        <v>62.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>15.9</v>
+        <v>66.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14.4</v>
+        <v>65.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>14.8</v>
+        <v>48.2</v>
       </c>
       <c r="AL11" t="n">
-        <v>13.3</v>
+        <v>56.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.2</v>
+        <v>55.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.9</v>
+        <v>55</v>
       </c>
       <c r="AO11" t="n">
-        <v>15.3</v>
+        <v>53.3</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>52.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.1</v>
+        <v>43.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.9</v>
+        <v>49.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.9</v>
+        <v>50.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>14.9</v>
+        <v>47.1</v>
       </c>
       <c r="AU11" t="n">
         <v>17.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>20.8</v>
@@ -19713,64 +19713,64 @@
         <v>28.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>55.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.1</v>
+        <v>53.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>15.9</v>
+        <v>58</v>
       </c>
       <c r="BB11" t="n">
         <v>23.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>15.2</v>
+        <v>60.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.2</v>
+        <v>68.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>16.6</v>
+        <v>61</v>
       </c>
       <c r="BF11" t="n">
-        <v>19.7</v>
+        <v>74.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>23</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.5</v>
+        <v>55.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>10.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="BJ11" t="n">
-        <v>18.1</v>
+        <v>63</v>
       </c>
       <c r="BK11" t="n">
-        <v>10.6</v>
+        <v>77.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>10.6</v>
+        <v>61.3</v>
       </c>
       <c r="BM11" t="n">
-        <v>18.8</v>
+        <v>48.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>20.9</v>
+        <v>64.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>17.3</v>
+        <v>47.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>16.1</v>
+        <v>65.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>15.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="BR11" t="n">
-        <v>10.1</v>
+        <v>54.8</v>
       </c>
       <c r="BS11" t="n">
         <v>20.5</v>
@@ -19779,91 +19779,91 @@
         <v>18.3</v>
       </c>
       <c r="BU11" t="n">
-        <v>9.9</v>
+        <v>55.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.3</v>
+        <v>57.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>21.6</v>
+        <v>64.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>9.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="BY11" t="n">
         <v>17.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>16.5</v>
+        <v>68.3</v>
       </c>
       <c r="CA11" t="n">
-        <v>18.5</v>
+        <v>55.4</v>
       </c>
       <c r="CB11" t="n">
-        <v>18.1</v>
+        <v>42.4</v>
       </c>
       <c r="CC11" t="n">
         <v>21.9</v>
       </c>
       <c r="CD11" t="n">
-        <v>11.4</v>
+        <v>53</v>
       </c>
       <c r="CE11" t="n">
-        <v>17.1</v>
+        <v>48.1</v>
       </c>
       <c r="CF11" t="n">
-        <v>15.8</v>
+        <v>52.7</v>
       </c>
       <c r="CG11" t="n">
         <v>21.2</v>
       </c>
       <c r="CH11" t="n">
-        <v>15.1</v>
+        <v>44.8</v>
       </c>
       <c r="CI11" t="n">
-        <v>17.1</v>
+        <v>52.8</v>
       </c>
       <c r="CJ11" t="n">
-        <v>19.5</v>
+        <v>64.7</v>
       </c>
       <c r="CK11" t="n">
-        <v>19.1</v>
+        <v>71.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>13.6</v>
+        <v>69.5</v>
       </c>
       <c r="CM11" t="n">
-        <v>12.6</v>
+        <v>84.5</v>
       </c>
       <c r="CN11" t="n">
-        <v>11.3</v>
+        <v>77.2</v>
       </c>
       <c r="CO11" t="n">
-        <v>15.7</v>
+        <v>69.7</v>
       </c>
       <c r="CP11" t="n">
-        <v>19.3</v>
+        <v>61.1</v>
       </c>
       <c r="CQ11" t="n">
-        <v>13.3</v>
+        <v>47.8</v>
       </c>
       <c r="CR11" t="n">
-        <v>20.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="CS11" t="n">
-        <v>11.1</v>
+        <v>57.2</v>
       </c>
       <c r="CT11" t="n">
-        <v>16.8</v>
+        <v>68.3</v>
       </c>
       <c r="CU11" t="n">
-        <v>14.2</v>
+        <v>55.6</v>
       </c>
       <c r="CV11" t="n">
-        <v>12.9</v>
+        <v>57.9</v>
       </c>
       <c r="CW11" t="n">
-        <v>16.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="12">
@@ -19879,13 +19879,13 @@
         <v>28.5</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>63.9</v>
       </c>
       <c r="E12" t="n">
         <v>26.1</v>
       </c>
       <c r="F12" t="n">
-        <v>16.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>25.8</v>
@@ -19894,16 +19894,16 @@
         <v>26.5</v>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>67.8</v>
       </c>
       <c r="J12" t="n">
-        <v>18.4</v>
+        <v>68</v>
       </c>
       <c r="K12" t="n">
-        <v>22.3</v>
+        <v>59.4</v>
       </c>
       <c r="L12" t="n">
-        <v>20.8</v>
+        <v>69.2</v>
       </c>
       <c r="M12" t="n">
         <v>24.4</v>
@@ -19918,13 +19918,13 @@
         <v>24.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>23.2</v>
+        <v>81.7</v>
       </c>
       <c r="R12" t="n">
-        <v>17.1</v>
+        <v>51.3</v>
       </c>
       <c r="S12" t="n">
-        <v>18.4</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>23.5</v>
@@ -19933,10 +19933,10 @@
         <v>32.2</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>53</v>
       </c>
       <c r="W12" t="n">
-        <v>13.9</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>28.5</v>
@@ -19945,13 +19945,13 @@
         <v>25.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.2</v>
+        <v>71</v>
       </c>
       <c r="AA12" t="n">
         <v>25.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>17.5</v>
+        <v>59.8</v>
       </c>
       <c r="AC12" t="n">
         <v>28.3</v>
@@ -19963,55 +19963,55 @@
         <v>24.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.4</v>
+        <v>58.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>54.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.8</v>
+        <v>58</v>
       </c>
       <c r="AI12" t="n">
         <v>26.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24.1</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>18.4</v>
+        <v>52.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>21.4</v>
+        <v>69.8</v>
       </c>
       <c r="AM12" t="n">
         <v>25</v>
       </c>
       <c r="AN12" t="n">
-        <v>21.2</v>
+        <v>87</v>
       </c>
       <c r="AO12" t="n">
-        <v>23.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>21.6</v>
+        <v>61.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>25.4</v>
+        <v>73.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.2</v>
+        <v>53.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>19.6</v>
+        <v>62.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>24.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>12.3</v>
+        <v>60.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>19.7</v>
+        <v>69.7</v>
       </c>
       <c r="AW12" t="n">
         <v>25.8</v>
@@ -20023,19 +20023,19 @@
         <v>26.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21.3</v>
+        <v>57.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>22.1</v>
+        <v>65.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>18.1</v>
+        <v>69.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>26.3</v>
+        <v>70</v>
       </c>
       <c r="BD12" t="n">
-        <v>24.4</v>
+        <v>75.5</v>
       </c>
       <c r="BE12" t="n">
         <v>22.8</v>
@@ -20044,13 +20044,13 @@
         <v>25.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>23.1</v>
+        <v>62.7</v>
       </c>
       <c r="BH12" t="n">
         <v>25.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>20.7</v>
+        <v>68</v>
       </c>
       <c r="BJ12" t="n">
         <v>28.2</v>
@@ -20062,7 +20062,7 @@
         <v>22.1</v>
       </c>
       <c r="BM12" t="n">
-        <v>22.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>26.2</v>
@@ -20074,7 +20074,7 @@
         <v>29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>17</v>
+        <v>46.8</v>
       </c>
       <c r="BR12" t="n">
         <v>23.9</v>
@@ -20083,16 +20083,16 @@
         <v>26.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>15.3</v>
+        <v>76.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="BV12" t="n">
-        <v>19.4</v>
+        <v>55.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>21.5</v>
+        <v>58.1</v>
       </c>
       <c r="BX12" t="n">
         <v>25.7</v>
@@ -20101,10 +20101,10 @@
         <v>23.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>22.1</v>
+        <v>84.8</v>
       </c>
       <c r="CA12" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="CB12" t="n">
         <v>24.7</v>
@@ -20116,13 +20116,13 @@
         <v>26.5</v>
       </c>
       <c r="CE12" t="n">
-        <v>13.5</v>
+        <v>58</v>
       </c>
       <c r="CF12" t="n">
-        <v>23.5</v>
+        <v>66.3</v>
       </c>
       <c r="CG12" t="n">
-        <v>18.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="CH12" t="n">
         <v>25.6</v>
@@ -20131,13 +20131,13 @@
         <v>26.3</v>
       </c>
       <c r="CJ12" t="n">
-        <v>19.7</v>
+        <v>64.2</v>
       </c>
       <c r="CK12" t="n">
-        <v>17.9</v>
+        <v>71.8</v>
       </c>
       <c r="CL12" t="n">
-        <v>17.9</v>
+        <v>76.7</v>
       </c>
       <c r="CM12" t="n">
         <v>26.2</v>
@@ -20146,13 +20146,13 @@
         <v>24.2</v>
       </c>
       <c r="CO12" t="n">
-        <v>19.6</v>
+        <v>52.2</v>
       </c>
       <c r="CP12" t="n">
         <v>26.4</v>
       </c>
       <c r="CQ12" t="n">
-        <v>23.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="CR12" t="n">
         <v>22.7</v>
@@ -20164,13 +20164,13 @@
         <v>24</v>
       </c>
       <c r="CU12" t="n">
-        <v>21.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="CV12" t="n">
-        <v>18.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="CW12" t="n">
-        <v>24.2</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="13">
@@ -20195,7 +20195,7 @@
         <v>35.1</v>
       </c>
       <c r="G13" t="n">
-        <v>28.5</v>
+        <v>75.7</v>
       </c>
       <c r="H13" t="n">
         <v>28.7</v>
@@ -20222,7 +20222,7 @@
         <v>29</v>
       </c>
       <c r="P13" t="n">
-        <v>25.8</v>
+        <v>84.2</v>
       </c>
       <c r="Q13" t="n">
         <v>38.7</v>
@@ -20231,7 +20231,7 @@
         <v>31.4</v>
       </c>
       <c r="S13" t="n">
-        <v>27.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>33.5</v>
@@ -20249,7 +20249,7 @@
         <v>36.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>27.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Z13" t="n">
         <v>37.5</v>
@@ -20270,7 +20270,7 @@
         <v>36.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>28.1</v>
+        <v>85</v>
       </c>
       <c r="AG13" t="n">
         <v>32.4</v>
@@ -20339,7 +20339,7 @@
         <v>44.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="BD13" t="n">
         <v>34.7</v>
@@ -20354,7 +20354,7 @@
         <v>39.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>28.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="BI13" t="n">
         <v>35</v>
@@ -20429,7 +20429,7 @@
         <v>32.4</v>
       </c>
       <c r="CG13" t="n">
-        <v>26.7</v>
+        <v>70.8</v>
       </c>
       <c r="CH13" t="n">
         <v>33.7</v>
@@ -20444,7 +20444,7 @@
         <v>28</v>
       </c>
       <c r="CL13" t="n">
-        <v>28</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="CM13" t="n">
         <v>35.2</v>
@@ -20487,304 +20487,304 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3</v>
+        <v>38.7</v>
       </c>
       <c r="C14" t="n">
-        <v>12.8</v>
+        <v>54.2</v>
       </c>
       <c r="D14" t="n">
-        <v>16.2</v>
+        <v>44.2</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>38.2</v>
       </c>
       <c r="F14" t="n">
-        <v>11.4</v>
+        <v>51.5</v>
       </c>
       <c r="G14" t="n">
-        <v>16.8</v>
+        <v>63.5</v>
       </c>
       <c r="H14" t="n">
-        <v>12.6</v>
+        <v>51</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>51</v>
       </c>
       <c r="J14" t="n">
-        <v>11.8</v>
+        <v>43.5</v>
       </c>
       <c r="K14" t="n">
-        <v>11.6</v>
+        <v>39.7</v>
       </c>
       <c r="L14" t="n">
-        <v>7.7</v>
+        <v>49.8</v>
       </c>
       <c r="M14" t="n">
         <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>13.4</v>
+        <v>49.6</v>
       </c>
       <c r="O14" t="n">
         <v>12.8</v>
       </c>
       <c r="P14" t="n">
-        <v>16.7</v>
+        <v>46.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.4</v>
+        <v>40.7</v>
       </c>
       <c r="R14" t="n">
-        <v>15.6</v>
+        <v>43</v>
       </c>
       <c r="S14" t="n">
-        <v>13.3</v>
+        <v>49.9</v>
       </c>
       <c r="T14" t="n">
-        <v>9.6</v>
+        <v>48.9</v>
       </c>
       <c r="U14" t="n">
-        <v>11.8</v>
+        <v>37.9</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>54.5</v>
       </c>
       <c r="W14" t="n">
-        <v>9.300000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="X14" t="n">
-        <v>8.4</v>
+        <v>50.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.4</v>
+        <v>49.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.6</v>
+        <v>53</v>
       </c>
       <c r="AA14" t="n">
-        <v>13</v>
+        <v>39.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.2</v>
+        <v>48.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.2</v>
+        <v>53.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>61.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>8.9</v>
+        <v>40.4</v>
       </c>
       <c r="AF14" t="n">
         <v>15.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.300000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>13.9</v>
+        <v>45</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>45.8</v>
       </c>
       <c r="AJ14" t="n">
         <v>16.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.5</v>
+        <v>56.4</v>
       </c>
       <c r="AL14" t="n">
-        <v>13.2</v>
+        <v>58.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>49.1</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.199999999999999</v>
+        <v>39.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>9.300000000000001</v>
+        <v>37.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.5</v>
+        <v>53.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.1</v>
+        <v>42.7</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.699999999999999</v>
+        <v>30.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.8</v>
+        <v>51.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>15.3</v>
+        <v>53.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>13.3</v>
+        <v>47.3</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.4</v>
+        <v>50.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.5</v>
+        <v>40.2</v>
       </c>
       <c r="AY14" t="n">
         <v>14.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.4</v>
+        <v>54.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>52.3</v>
       </c>
       <c r="BB14" t="n">
         <v>16.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>10.9</v>
+        <v>50.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>44.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.800000000000001</v>
+        <v>38.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>52.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>11.3</v>
+        <v>48.7</v>
       </c>
       <c r="BH14" t="n">
-        <v>13</v>
+        <v>55.9</v>
       </c>
       <c r="BI14" t="n">
         <v>15.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>14.1</v>
+        <v>34</v>
       </c>
       <c r="BK14" t="n">
-        <v>8.9</v>
+        <v>26.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>6.3</v>
+        <v>41.4</v>
       </c>
       <c r="BM14" t="n">
-        <v>12.5</v>
+        <v>55.9</v>
       </c>
       <c r="BN14" t="n">
-        <v>14.1</v>
+        <v>65.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>10.7</v>
+        <v>51.4</v>
       </c>
       <c r="BP14" t="n">
         <v>17.9</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.1</v>
+        <v>60.4</v>
       </c>
       <c r="BR14" t="n">
-        <v>5.6</v>
+        <v>44</v>
       </c>
       <c r="BS14" t="n">
         <v>14.9</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.4</v>
+        <v>42.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>8.800000000000001</v>
+        <v>49.2</v>
       </c>
       <c r="BV14" t="n">
         <v>19.8</v>
       </c>
       <c r="BW14" t="n">
-        <v>10.2</v>
+        <v>45.1</v>
       </c>
       <c r="BX14" t="n">
-        <v>16.1</v>
+        <v>58.4</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.1</v>
+        <v>57.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>16.9</v>
+        <v>42.4</v>
       </c>
       <c r="CA14" t="n">
-        <v>10.1</v>
+        <v>54.2</v>
       </c>
       <c r="CB14" t="n">
         <v>18.9</v>
       </c>
       <c r="CC14" t="n">
-        <v>9.699999999999999</v>
+        <v>47.4</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.8</v>
+        <v>45.7</v>
       </c>
       <c r="CE14" t="n">
-        <v>7.4</v>
+        <v>46.7</v>
       </c>
       <c r="CF14" t="n">
-        <v>11.6</v>
+        <v>57.9</v>
       </c>
       <c r="CG14" t="n">
-        <v>15.3</v>
+        <v>51.1</v>
       </c>
       <c r="CH14" t="n">
-        <v>10.2</v>
+        <v>59.6</v>
       </c>
       <c r="CI14" t="n">
-        <v>7</v>
+        <v>37.6</v>
       </c>
       <c r="CJ14" t="n">
-        <v>6.4</v>
+        <v>43.3</v>
       </c>
       <c r="CK14" t="n">
-        <v>12.7</v>
+        <v>58.9</v>
       </c>
       <c r="CL14" t="n">
-        <v>12.6</v>
+        <v>48.9</v>
       </c>
       <c r="CM14" t="n">
-        <v>16.4</v>
+        <v>43.3</v>
       </c>
       <c r="CN14" t="n">
-        <v>14.1</v>
+        <v>54</v>
       </c>
       <c r="CO14" t="n">
-        <v>3.6</v>
+        <v>31.4</v>
       </c>
       <c r="CP14" t="n">
-        <v>9.4</v>
+        <v>49.2</v>
       </c>
       <c r="CQ14" t="n">
-        <v>7.8</v>
+        <v>45.8</v>
       </c>
       <c r="CR14" t="n">
-        <v>5.8</v>
+        <v>35.1</v>
       </c>
       <c r="CS14" t="n">
-        <v>8.699999999999999</v>
+        <v>35.7</v>
       </c>
       <c r="CT14" t="n">
-        <v>10.8</v>
+        <v>65.8</v>
       </c>
       <c r="CU14" t="n">
         <v>15.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>9.5</v>
+        <v>56.3</v>
       </c>
       <c r="CW14" t="n">
-        <v>16.1</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="15">
@@ -20869,16 +20869,16 @@
         <v>33.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>18.4</v>
+        <v>55.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>20.6</v>
+        <v>62.6</v>
       </c>
       <c r="AC15" t="n">
         <v>29.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.6</v>
+        <v>72.2</v>
       </c>
       <c r="AE15" t="n">
         <v>26.6</v>
@@ -20905,7 +20905,7 @@
         <v>27.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>18.1</v>
+        <v>63.3</v>
       </c>
       <c r="AN15" t="n">
         <v>33.2</v>
@@ -20935,7 +20935,7 @@
         <v>21.9</v>
       </c>
       <c r="AW15" t="n">
-        <v>18.1</v>
+        <v>53.8</v>
       </c>
       <c r="AX15" t="n">
         <v>28.9</v>
@@ -20995,7 +20995,7 @@
         <v>31.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>14.7</v>
+        <v>55</v>
       </c>
       <c r="BR15" t="n">
         <v>30.9</v>
@@ -21004,7 +21004,7 @@
         <v>34.1</v>
       </c>
       <c r="BT15" t="n">
-        <v>16.2</v>
+        <v>43.3</v>
       </c>
       <c r="BU15" t="n">
         <v>30.5</v>
@@ -21067,7 +21067,7 @@
         <v>25.8</v>
       </c>
       <c r="CO15" t="n">
-        <v>20.3</v>
+        <v>63.2</v>
       </c>
       <c r="CP15" t="n">
         <v>38.6</v>
@@ -21076,7 +21076,7 @@
         <v>24.7</v>
       </c>
       <c r="CR15" t="n">
-        <v>18.9</v>
+        <v>53.7</v>
       </c>
       <c r="CS15" t="n">
         <v>21.3</v>
@@ -21215,7 +21215,7 @@
         <v>32.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>19.9</v>
+        <v>54.7</v>
       </c>
       <c r="AO16" t="n">
         <v>28.6</v>
@@ -21230,7 +21230,7 @@
         <v>30.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>21.6</v>
+        <v>61.4</v>
       </c>
       <c r="AT16" t="n">
         <v>22.9</v>
@@ -21302,10 +21302,10 @@
         <v>30.6</v>
       </c>
       <c r="BQ16" t="n">
-        <v>19.8</v>
+        <v>65</v>
       </c>
       <c r="BR16" t="n">
-        <v>20.4</v>
+        <v>62.4</v>
       </c>
       <c r="BS16" t="n">
         <v>34.8</v>
@@ -21383,7 +21383,7 @@
         <v>27.8</v>
       </c>
       <c r="CR16" t="n">
-        <v>22.4</v>
+        <v>67.5</v>
       </c>
       <c r="CS16" t="n">
         <v>40.4</v>
@@ -21392,7 +21392,7 @@
         <v>38.2</v>
       </c>
       <c r="CU16" t="n">
-        <v>21.6</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="CV16" t="n">
         <v>31.8</v>
@@ -22058,7 +22058,7 @@
         <v>25.2</v>
       </c>
       <c r="N19" t="n">
-        <v>12.3</v>
+        <v>35.2</v>
       </c>
       <c r="O19" t="n">
         <v>29.7</v>
@@ -22184,7 +22184,7 @@
         <v>27.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.6</v>
+        <v>61.1</v>
       </c>
       <c r="BE19" t="n">
         <v>28.7</v>
@@ -23334,7 +23334,7 @@
         <v>28</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.1</v>
+        <v>47.9</v>
       </c>
       <c r="AE23" t="n">
         <v>21.3</v>
@@ -24493,7 +24493,7 @@
         <v>26.3</v>
       </c>
       <c r="G27" t="n">
-        <v>21</v>
+        <v>61.5</v>
       </c>
       <c r="H27" t="n">
         <v>38.1</v>
@@ -24628,7 +24628,7 @@
         <v>39.2</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21.1</v>
+        <v>62.8</v>
       </c>
       <c r="BA27" t="n">
         <v>29.4</v>
@@ -24700,7 +24700,7 @@
         <v>38.1</v>
       </c>
       <c r="BX27" t="n">
-        <v>22.4</v>
+        <v>66.5</v>
       </c>
       <c r="BY27" t="n">
         <v>29.8</v>
@@ -24763,7 +24763,7 @@
         <v>24.6</v>
       </c>
       <c r="CS27" t="n">
-        <v>18.1</v>
+        <v>59.9</v>
       </c>
       <c r="CT27" t="n">
         <v>28.5</v>
@@ -25856,7 +25856,7 @@
         <v>27.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17.1</v>
+        <v>47.2</v>
       </c>
       <c r="BA31" t="n">
         <v>30.3</v>
@@ -26013,235 +26013,235 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.7</v>
+        <v>40.9</v>
       </c>
       <c r="C32" t="n">
-        <v>5.4</v>
+        <v>46.2</v>
       </c>
       <c r="D32" t="n">
         <v>16.6</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>55.1</v>
       </c>
       <c r="F32" t="n">
         <v>11.9</v>
       </c>
       <c r="G32" t="n">
-        <v>9.5</v>
+        <v>33.5</v>
       </c>
       <c r="H32" t="n">
-        <v>10.6</v>
+        <v>53.7</v>
       </c>
       <c r="I32" t="n">
-        <v>7.7</v>
+        <v>30.9</v>
       </c>
       <c r="J32" t="n">
-        <v>9.6</v>
+        <v>30.5</v>
       </c>
       <c r="K32" t="n">
-        <v>6.9</v>
+        <v>48</v>
       </c>
       <c r="L32" t="n">
-        <v>11.5</v>
+        <v>41.2</v>
       </c>
       <c r="M32" t="n">
         <v>20.2</v>
       </c>
       <c r="N32" t="n">
-        <v>4.4</v>
+        <v>45.6</v>
       </c>
       <c r="O32" t="n">
-        <v>3.9</v>
+        <v>48.9</v>
       </c>
       <c r="P32" t="n">
-        <v>7.5</v>
+        <v>41.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.4</v>
+        <v>44</v>
       </c>
       <c r="R32" t="n">
-        <v>8.699999999999999</v>
+        <v>33.6</v>
       </c>
       <c r="S32" t="n">
-        <v>11.4</v>
+        <v>47.8</v>
       </c>
       <c r="T32" t="n">
-        <v>13.8</v>
+        <v>45.7</v>
       </c>
       <c r="U32" t="n">
-        <v>7.1</v>
+        <v>31.9</v>
       </c>
       <c r="V32" t="n">
-        <v>13.3</v>
+        <v>49.6</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>47.6</v>
       </c>
       <c r="X32" t="n">
         <v>14.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>10.8</v>
+        <v>43.9</v>
       </c>
       <c r="Z32" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.800000000000001</v>
+        <v>31.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.3</v>
+        <v>43.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.2</v>
+        <v>39.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>6.9</v>
+        <v>31.9</v>
       </c>
       <c r="AE32" t="n">
-        <v>12.1</v>
+        <v>40.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>12.9</v>
+        <v>48.7</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>37.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.6</v>
+        <v>38.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>11.2</v>
+        <v>53.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>15.6</v>
+        <v>42.4</v>
       </c>
       <c r="AK32" t="n">
-        <v>9.300000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="AL32" t="n">
-        <v>9.9</v>
+        <v>43.6</v>
       </c>
       <c r="AM32" t="n">
-        <v>14.8</v>
+        <v>48.4</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.9</v>
+        <v>40.4</v>
       </c>
       <c r="AO32" t="n">
-        <v>7.5</v>
+        <v>33.8</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.7</v>
+        <v>33.1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>11.3</v>
+        <v>44.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>7.2</v>
+        <v>27.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>9.5</v>
+        <v>53.8</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.8</v>
+        <v>49.7</v>
       </c>
       <c r="AU32" t="n">
-        <v>8.199999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>11.3</v>
+        <v>52.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.9</v>
+        <v>42.8</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>41.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>7</v>
+        <v>34.3</v>
       </c>
       <c r="AZ32" t="n">
         <v>16.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.5</v>
+        <v>35.3</v>
       </c>
       <c r="BB32" t="n">
-        <v>14.5</v>
+        <v>32.8</v>
       </c>
       <c r="BC32" t="n">
-        <v>10.7</v>
+        <v>39.5</v>
       </c>
       <c r="BD32" t="n">
         <v>14.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>13.7</v>
+        <v>45.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.5</v>
+        <v>47</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.7</v>
+        <v>38.9</v>
       </c>
       <c r="BH32" t="n">
-        <v>3.3</v>
+        <v>39.7</v>
       </c>
       <c r="BI32" t="n">
-        <v>12.2</v>
+        <v>43.4</v>
       </c>
       <c r="BJ32" t="n">
-        <v>8.300000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="BK32" t="n">
-        <v>7.2</v>
+        <v>34.7</v>
       </c>
       <c r="BL32" t="n">
-        <v>8.1</v>
+        <v>37.2</v>
       </c>
       <c r="BM32" t="n">
         <v>14.1</v>
       </c>
       <c r="BN32" t="n">
-        <v>2.9</v>
+        <v>27.5</v>
       </c>
       <c r="BO32" t="n">
-        <v>5.8</v>
+        <v>48.7</v>
       </c>
       <c r="BP32" t="n">
-        <v>8.6</v>
+        <v>33.7</v>
       </c>
       <c r="BQ32" t="n">
-        <v>10.7</v>
+        <v>50.1</v>
       </c>
       <c r="BR32" t="n">
-        <v>8.699999999999999</v>
+        <v>32.4</v>
       </c>
       <c r="BS32" t="n">
-        <v>9.9</v>
+        <v>31.8</v>
       </c>
       <c r="BT32" t="n">
-        <v>9.9</v>
+        <v>45.7</v>
       </c>
       <c r="BU32" t="n">
-        <v>10.3</v>
+        <v>57.7</v>
       </c>
       <c r="BV32" t="n">
-        <v>6.6</v>
+        <v>33</v>
       </c>
       <c r="BW32" t="n">
-        <v>4.8</v>
+        <v>33.2</v>
       </c>
       <c r="BX32" t="n">
-        <v>7.5</v>
+        <v>25.8</v>
       </c>
       <c r="BY32" t="n">
         <v>13.1</v>
       </c>
       <c r="BZ32" t="n">
-        <v>11.1</v>
+        <v>46.7</v>
       </c>
       <c r="CA32" t="n">
         <v>10.9</v>
@@ -26256,46 +26256,46 @@
         <v>16.6</v>
       </c>
       <c r="CE32" t="n">
-        <v>6.5</v>
+        <v>40.6</v>
       </c>
       <c r="CF32" t="n">
         <v>15.4</v>
       </c>
       <c r="CG32" t="n">
-        <v>5.8</v>
+        <v>34.9</v>
       </c>
       <c r="CH32" t="n">
-        <v>11.8</v>
+        <v>40.9</v>
       </c>
       <c r="CI32" t="n">
-        <v>3.5</v>
+        <v>44.7</v>
       </c>
       <c r="CJ32" t="n">
-        <v>8.199999999999999</v>
+        <v>30.7</v>
       </c>
       <c r="CK32" t="n">
-        <v>4.8</v>
+        <v>40.8</v>
       </c>
       <c r="CL32" t="n">
         <v>18.5</v>
       </c>
       <c r="CM32" t="n">
-        <v>9.199999999999999</v>
+        <v>42.4</v>
       </c>
       <c r="CN32" t="n">
-        <v>9.800000000000001</v>
+        <v>46.6</v>
       </c>
       <c r="CO32" t="n">
-        <v>14.8</v>
+        <v>59.7</v>
       </c>
       <c r="CP32" t="n">
-        <v>8.199999999999999</v>
+        <v>34.1</v>
       </c>
       <c r="CQ32" t="n">
-        <v>12</v>
+        <v>41.8</v>
       </c>
       <c r="CR32" t="n">
-        <v>7.5</v>
+        <v>29.3</v>
       </c>
       <c r="CS32" t="n">
         <v>13.3</v>
@@ -26304,13 +26304,13 @@
         <v>17</v>
       </c>
       <c r="CU32" t="n">
-        <v>13.7</v>
+        <v>42.5</v>
       </c>
       <c r="CV32" t="n">
-        <v>10.3</v>
+        <v>31.5</v>
       </c>
       <c r="CW32" t="n">
-        <v>9.800000000000001</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="33">
@@ -28776,82 +28776,82 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>18.5</v>
+        <v>55.9</v>
       </c>
       <c r="C41" t="n">
-        <v>6.4</v>
+        <v>61.8</v>
       </c>
       <c r="D41" t="n">
-        <v>19.1</v>
+        <v>43.9</v>
       </c>
       <c r="E41" t="n">
         <v>19.6</v>
       </c>
       <c r="F41" t="n">
-        <v>10.6</v>
+        <v>58.7</v>
       </c>
       <c r="G41" t="n">
         <v>20.9</v>
       </c>
       <c r="H41" t="n">
-        <v>16</v>
+        <v>53.1</v>
       </c>
       <c r="I41" t="n">
         <v>22.2</v>
       </c>
       <c r="J41" t="n">
-        <v>15.8</v>
+        <v>72</v>
       </c>
       <c r="K41" t="n">
-        <v>15</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>17.6</v>
+        <v>47.7</v>
       </c>
       <c r="M41" t="n">
-        <v>14.7</v>
+        <v>65.5</v>
       </c>
       <c r="N41" t="n">
         <v>19.2</v>
       </c>
       <c r="O41" t="n">
-        <v>11.5</v>
+        <v>62.4</v>
       </c>
       <c r="P41" t="n">
         <v>22.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>16.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R41" t="n">
         <v>22.6</v>
       </c>
       <c r="S41" t="n">
-        <v>20.8</v>
+        <v>65.7</v>
       </c>
       <c r="T41" t="n">
-        <v>18.2</v>
+        <v>52</v>
       </c>
       <c r="U41" t="n">
-        <v>17.4</v>
+        <v>54.3</v>
       </c>
       <c r="V41" t="n">
-        <v>22.1</v>
+        <v>54.9</v>
       </c>
       <c r="W41" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="X41" t="n">
-        <v>20.5</v>
+        <v>63.3</v>
       </c>
       <c r="Y41" t="n">
         <v>30.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>11.6</v>
+        <v>52.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>14.8</v>
+        <v>60.6</v>
       </c>
       <c r="AB41" t="n">
         <v>22.9</v>
@@ -28863,25 +28863,25 @@
         <v>23</v>
       </c>
       <c r="AE41" t="n">
-        <v>19.9</v>
+        <v>61.7</v>
       </c>
       <c r="AF41" t="n">
         <v>23</v>
       </c>
       <c r="AG41" t="n">
-        <v>20.5</v>
+        <v>50.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>11.4</v>
+        <v>63</v>
       </c>
       <c r="AI41" t="n">
         <v>24.7</v>
       </c>
       <c r="AJ41" t="n">
-        <v>20.9</v>
+        <v>54.6</v>
       </c>
       <c r="AK41" t="n">
-        <v>15.5</v>
+        <v>55.5</v>
       </c>
       <c r="AL41" t="n">
         <v>30.6</v>
@@ -28890,13 +28890,13 @@
         <v>20.8</v>
       </c>
       <c r="AN41" t="n">
-        <v>20</v>
+        <v>57.8</v>
       </c>
       <c r="AO41" t="n">
-        <v>18.2</v>
+        <v>47.9</v>
       </c>
       <c r="AP41" t="n">
-        <v>18.2</v>
+        <v>65.3</v>
       </c>
       <c r="AQ41" t="n">
         <v>22.2</v>
@@ -28905,7 +28905,7 @@
         <v>19.1</v>
       </c>
       <c r="AS41" t="n">
-        <v>20.3</v>
+        <v>50.9</v>
       </c>
       <c r="AT41" t="n">
         <v>23.3</v>
@@ -28914,13 +28914,13 @@
         <v>26.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>16.6</v>
+        <v>59.8</v>
       </c>
       <c r="AW41" t="n">
-        <v>13</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AX41" t="n">
-        <v>21.3</v>
+        <v>56.3</v>
       </c>
       <c r="AY41" t="n">
         <v>22</v>
@@ -28929,49 +28929,49 @@
         <v>21.7</v>
       </c>
       <c r="BA41" t="n">
-        <v>21</v>
+        <v>55.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>18.7</v>
+        <v>66.8</v>
       </c>
       <c r="BC41" t="n">
-        <v>11.4</v>
+        <v>42.6</v>
       </c>
       <c r="BD41" t="n">
         <v>21.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>17.1</v>
+        <v>69.7</v>
       </c>
       <c r="BF41" t="n">
         <v>18</v>
       </c>
       <c r="BG41" t="n">
-        <v>17.5</v>
+        <v>42.9</v>
       </c>
       <c r="BH41" t="n">
         <v>16.1</v>
       </c>
       <c r="BI41" t="n">
-        <v>17.2</v>
+        <v>50.1</v>
       </c>
       <c r="BJ41" t="n">
-        <v>16.3</v>
+        <v>56.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>22.1</v>
+        <v>54.7</v>
       </c>
       <c r="BL41" t="n">
-        <v>13.1</v>
+        <v>62.5</v>
       </c>
       <c r="BM41" t="n">
-        <v>15.1</v>
+        <v>46</v>
       </c>
       <c r="BN41" t="n">
-        <v>18.1</v>
+        <v>49.8</v>
       </c>
       <c r="BO41" t="n">
-        <v>19.7</v>
+        <v>65.5</v>
       </c>
       <c r="BP41" t="n">
         <v>20.8</v>
@@ -28983,58 +28983,58 @@
         <v>22.6</v>
       </c>
       <c r="BS41" t="n">
-        <v>17.2</v>
+        <v>54.8</v>
       </c>
       <c r="BT41" t="n">
-        <v>19.7</v>
+        <v>62.5</v>
       </c>
       <c r="BU41" t="n">
-        <v>19.4</v>
+        <v>49.7</v>
       </c>
       <c r="BV41" t="n">
         <v>27.1</v>
       </c>
       <c r="BW41" t="n">
-        <v>16.6</v>
+        <v>49.3</v>
       </c>
       <c r="BX41" t="n">
-        <v>10.4</v>
+        <v>64.3</v>
       </c>
       <c r="BY41" t="n">
         <v>27.3</v>
       </c>
       <c r="BZ41" t="n">
-        <v>17.3</v>
+        <v>52</v>
       </c>
       <c r="CA41" t="n">
         <v>21.2</v>
       </c>
       <c r="CB41" t="n">
-        <v>18.1</v>
+        <v>56.2</v>
       </c>
       <c r="CC41" t="n">
-        <v>19.9</v>
+        <v>59.8</v>
       </c>
       <c r="CD41" t="n">
-        <v>14.4</v>
+        <v>71.3</v>
       </c>
       <c r="CE41" t="n">
         <v>25.8</v>
       </c>
       <c r="CF41" t="n">
-        <v>12.3</v>
+        <v>64</v>
       </c>
       <c r="CG41" t="n">
-        <v>22.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="CH41" t="n">
-        <v>15.9</v>
+        <v>47.8</v>
       </c>
       <c r="CI41" t="n">
-        <v>20.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="CJ41" t="n">
-        <v>14.7</v>
+        <v>51.4</v>
       </c>
       <c r="CK41" t="n">
         <v>24.1</v>
@@ -29043,34 +29043,34 @@
         <v>22.1</v>
       </c>
       <c r="CM41" t="n">
-        <v>17.8</v>
+        <v>62.7</v>
       </c>
       <c r="CN41" t="n">
-        <v>19.2</v>
+        <v>78.8</v>
       </c>
       <c r="CO41" t="n">
-        <v>18.9</v>
+        <v>54.7</v>
       </c>
       <c r="CP41" t="n">
-        <v>19.2</v>
+        <v>55.9</v>
       </c>
       <c r="CQ41" t="n">
-        <v>13.8</v>
+        <v>65</v>
       </c>
       <c r="CR41" t="n">
-        <v>14.6</v>
+        <v>55.7</v>
       </c>
       <c r="CS41" t="n">
-        <v>15.4</v>
+        <v>54.3</v>
       </c>
       <c r="CT41" t="n">
-        <v>18.2</v>
+        <v>52</v>
       </c>
       <c r="CU41" t="n">
         <v>21.1</v>
       </c>
       <c r="CV41" t="n">
-        <v>16.1</v>
+        <v>69.2</v>
       </c>
       <c r="CW41" t="n">
         <v>20.6</v>
@@ -29086,115 +29086,115 @@
         <v>14.9</v>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>56.3</v>
       </c>
       <c r="D42" t="n">
-        <v>23.6</v>
+        <v>72.7</v>
       </c>
       <c r="E42" t="n">
         <v>28.2</v>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>58.5</v>
       </c>
       <c r="G42" t="n">
-        <v>20.5</v>
+        <v>51.9</v>
       </c>
       <c r="H42" t="n">
         <v>21.6</v>
       </c>
       <c r="I42" t="n">
-        <v>19.4</v>
+        <v>61.2</v>
       </c>
       <c r="J42" t="n">
-        <v>15.2</v>
+        <v>52.1</v>
       </c>
       <c r="K42" t="n">
         <v>22.7</v>
       </c>
       <c r="L42" t="n">
-        <v>18.8</v>
+        <v>50.8</v>
       </c>
       <c r="M42" t="n">
         <v>20.9</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>14.2</v>
+        <v>66</v>
       </c>
       <c r="P42" t="n">
-        <v>18.6</v>
+        <v>54</v>
       </c>
       <c r="Q42" t="n">
-        <v>19.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="R42" t="n">
-        <v>20.3</v>
+        <v>57.1</v>
       </c>
       <c r="S42" t="n">
-        <v>18.9</v>
+        <v>60.6</v>
       </c>
       <c r="T42" t="n">
         <v>22.5</v>
       </c>
       <c r="U42" t="n">
-        <v>15.7</v>
+        <v>59.9</v>
       </c>
       <c r="V42" t="n">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="W42" t="n">
-        <v>20.5</v>
+        <v>61</v>
       </c>
       <c r="X42" t="n">
-        <v>27.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Y42" t="n">
-        <v>13</v>
+        <v>51.3</v>
       </c>
       <c r="Z42" t="n">
         <v>21.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>9.6</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AB42" t="n">
-        <v>16.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AC42" t="n">
-        <v>18.8</v>
+        <v>50.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>19.2</v>
+        <v>57.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>20.4</v>
+        <v>63.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>15.7</v>
+        <v>53.3</v>
       </c>
       <c r="AG42" t="n">
-        <v>21.7</v>
+        <v>61.1</v>
       </c>
       <c r="AH42" t="n">
-        <v>16.4</v>
+        <v>54.1</v>
       </c>
       <c r="AI42" t="n">
-        <v>20.2</v>
+        <v>60.9</v>
       </c>
       <c r="AJ42" t="n">
-        <v>21.8</v>
+        <v>63.8</v>
       </c>
       <c r="AK42" t="n">
-        <v>14.2</v>
+        <v>62.6</v>
       </c>
       <c r="AL42" t="n">
-        <v>12.7</v>
+        <v>53</v>
       </c>
       <c r="AM42" t="n">
-        <v>13.8</v>
+        <v>49.3</v>
       </c>
       <c r="AN42" t="n">
         <v>26.5</v>
@@ -29206,37 +29206,37 @@
         <v>23.9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>20.3</v>
+        <v>69.7</v>
       </c>
       <c r="AR42" t="n">
-        <v>17.5</v>
+        <v>58.6</v>
       </c>
       <c r="AS42" t="n">
-        <v>18.2</v>
+        <v>61.6</v>
       </c>
       <c r="AT42" t="n">
-        <v>15.8</v>
+        <v>55.1</v>
       </c>
       <c r="AU42" t="n">
         <v>20.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>13.2</v>
+        <v>59.4</v>
       </c>
       <c r="AW42" t="n">
-        <v>18</v>
+        <v>66.8</v>
       </c>
       <c r="AX42" t="n">
-        <v>14.8</v>
+        <v>75.2</v>
       </c>
       <c r="AY42" t="n">
-        <v>16.4</v>
+        <v>54.9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>16.9</v>
+        <v>70</v>
       </c>
       <c r="BA42" t="n">
-        <v>18.8</v>
+        <v>54.7</v>
       </c>
       <c r="BB42" t="n">
         <v>24.3</v>
@@ -29245,91 +29245,91 @@
         <v>27.1</v>
       </c>
       <c r="BD42" t="n">
-        <v>18.4</v>
+        <v>63.1</v>
       </c>
       <c r="BE42" t="n">
-        <v>16.4</v>
+        <v>53.2</v>
       </c>
       <c r="BF42" t="n">
         <v>26.1</v>
       </c>
       <c r="BG42" t="n">
-        <v>13.7</v>
+        <v>54.6</v>
       </c>
       <c r="BH42" t="n">
-        <v>18.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="BI42" t="n">
         <v>25.8</v>
       </c>
       <c r="BJ42" t="n">
-        <v>14.7</v>
+        <v>68.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>15.3</v>
+        <v>59.9</v>
       </c>
       <c r="BL42" t="n">
-        <v>18.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="BM42" t="n">
-        <v>20.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="BN42" t="n">
-        <v>17.2</v>
+        <v>54.8</v>
       </c>
       <c r="BO42" t="n">
-        <v>20.6</v>
+        <v>59.8</v>
       </c>
       <c r="BP42" t="n">
-        <v>18.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="BQ42" t="n">
-        <v>15.9</v>
+        <v>53</v>
       </c>
       <c r="BR42" t="n">
-        <v>22.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="BS42" t="n">
-        <v>18.5</v>
+        <v>49.2</v>
       </c>
       <c r="BT42" t="n">
-        <v>24.5</v>
+        <v>59.4</v>
       </c>
       <c r="BU42" t="n">
         <v>26.9</v>
       </c>
       <c r="BV42" t="n">
-        <v>19.6</v>
+        <v>72.7</v>
       </c>
       <c r="BW42" t="n">
         <v>21.4</v>
       </c>
       <c r="BX42" t="n">
-        <v>20.2</v>
+        <v>55.6</v>
       </c>
       <c r="BY42" t="n">
-        <v>16.1</v>
+        <v>64.8</v>
       </c>
       <c r="BZ42" t="n">
-        <v>16.5</v>
+        <v>68</v>
       </c>
       <c r="CA42" t="n">
-        <v>17.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="CB42" t="n">
-        <v>19.1</v>
+        <v>62.2</v>
       </c>
       <c r="CC42" t="n">
         <v>19.1</v>
       </c>
       <c r="CD42" t="n">
-        <v>15.3</v>
+        <v>66.7</v>
       </c>
       <c r="CE42" t="n">
         <v>25.5</v>
       </c>
       <c r="CF42" t="n">
-        <v>18.9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="CG42" t="n">
         <v>26</v>
@@ -29338,10 +29338,10 @@
         <v>23.6</v>
       </c>
       <c r="CI42" t="n">
-        <v>14.5</v>
+        <v>62.5</v>
       </c>
       <c r="CJ42" t="n">
-        <v>13</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="CK42" t="n">
         <v>22.4</v>
@@ -29350,37 +29350,37 @@
         <v>19.3</v>
       </c>
       <c r="CM42" t="n">
-        <v>17.5</v>
+        <v>59</v>
       </c>
       <c r="CN42" t="n">
-        <v>15.4</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="CO42" t="n">
         <v>26.9</v>
       </c>
       <c r="CP42" t="n">
-        <v>17.8</v>
+        <v>71.8</v>
       </c>
       <c r="CQ42" t="n">
-        <v>15.3</v>
+        <v>65.3</v>
       </c>
       <c r="CR42" t="n">
-        <v>14.9</v>
+        <v>44.4</v>
       </c>
       <c r="CS42" t="n">
-        <v>20.8</v>
+        <v>70.3</v>
       </c>
       <c r="CT42" t="n">
         <v>16.3</v>
       </c>
       <c r="CU42" t="n">
-        <v>16</v>
+        <v>51.4</v>
       </c>
       <c r="CV42" t="n">
-        <v>21.7</v>
+        <v>56.8</v>
       </c>
       <c r="CW42" t="n">
-        <v>18.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="43">
@@ -29724,7 +29724,7 @@
         <v>23.4</v>
       </c>
       <c r="K44" t="n">
-        <v>19.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>22.9</v>
@@ -29739,7 +29739,7 @@
         <v>27.1</v>
       </c>
       <c r="P44" t="n">
-        <v>19.7</v>
+        <v>57.3</v>
       </c>
       <c r="Q44" t="n">
         <v>22.5</v>
@@ -29790,7 +29790,7 @@
         <v>21.3</v>
       </c>
       <c r="AG44" t="n">
-        <v>20.7</v>
+        <v>56.3</v>
       </c>
       <c r="AH44" t="n">
         <v>18.8</v>
@@ -29844,7 +29844,7 @@
         <v>24.7</v>
       </c>
       <c r="AY44" t="n">
-        <v>18.4</v>
+        <v>48.6</v>
       </c>
       <c r="AZ44" t="n">
         <v>25.2</v>
@@ -29856,7 +29856,7 @@
         <v>22.1</v>
       </c>
       <c r="BC44" t="n">
-        <v>17.9</v>
+        <v>59.4</v>
       </c>
       <c r="BD44" t="n">
         <v>27.1</v>
@@ -29871,7 +29871,7 @@
         <v>29.3</v>
       </c>
       <c r="BH44" t="n">
-        <v>17.1</v>
+        <v>39.6</v>
       </c>
       <c r="BI44" t="n">
         <v>29</v>
@@ -29889,7 +29889,7 @@
         <v>25.8</v>
       </c>
       <c r="BN44" t="n">
-        <v>14</v>
+        <v>54.4</v>
       </c>
       <c r="BO44" t="n">
         <v>23.6</v>
@@ -30642,13 +30642,13 @@
         <v>29.4</v>
       </c>
       <c r="J47" t="n">
-        <v>22.2</v>
+        <v>61.8</v>
       </c>
       <c r="K47" t="n">
         <v>29.8</v>
       </c>
       <c r="L47" t="n">
-        <v>23.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>30</v>
@@ -30672,7 +30672,7 @@
         <v>29.5</v>
       </c>
       <c r="T47" t="n">
-        <v>23.5</v>
+        <v>61.6</v>
       </c>
       <c r="U47" t="n">
         <v>26.1</v>
@@ -30696,22 +30696,22 @@
         <v>27.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>25.5</v>
+        <v>71.2</v>
       </c>
       <c r="AC47" t="n">
         <v>21.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>23.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AE47" t="n">
-        <v>18.6</v>
+        <v>62</v>
       </c>
       <c r="AF47" t="n">
         <v>38.1</v>
       </c>
       <c r="AG47" t="n">
-        <v>26.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AH47" t="n">
         <v>30.3</v>
@@ -30732,10 +30732,10 @@
         <v>24.9</v>
       </c>
       <c r="AN47" t="n">
-        <v>11</v>
+        <v>60.2</v>
       </c>
       <c r="AO47" t="n">
-        <v>20.8</v>
+        <v>58.1</v>
       </c>
       <c r="AP47" t="n">
         <v>25.8</v>
@@ -30753,7 +30753,7 @@
         <v>31.7</v>
       </c>
       <c r="AU47" t="n">
-        <v>17.5</v>
+        <v>63.6</v>
       </c>
       <c r="AV47" t="n">
         <v>27.5</v>
@@ -30762,7 +30762,7 @@
         <v>29.8</v>
       </c>
       <c r="AX47" t="n">
-        <v>17.8</v>
+        <v>63.4</v>
       </c>
       <c r="AY47" t="n">
         <v>28.3</v>
@@ -30786,7 +30786,7 @@
         <v>33.6</v>
       </c>
       <c r="BF47" t="n">
-        <v>25.5</v>
+        <v>79.5</v>
       </c>
       <c r="BG47" t="n">
         <v>21.6</v>
@@ -30837,7 +30837,7 @@
         <v>29.7</v>
       </c>
       <c r="BW47" t="n">
-        <v>21</v>
+        <v>63.4</v>
       </c>
       <c r="BX47" t="n">
         <v>27.1</v>
@@ -30882,7 +30882,7 @@
         <v>28.5</v>
       </c>
       <c r="CL47" t="n">
-        <v>20.5</v>
+        <v>60.5</v>
       </c>
       <c r="CM47" t="n">
         <v>24.7</v>
@@ -30909,7 +30909,7 @@
         <v>21.4</v>
       </c>
       <c r="CU47" t="n">
-        <v>18.9</v>
+        <v>53</v>
       </c>
       <c r="CV47" t="n">
         <v>38.8</v>
@@ -31235,10 +31235,10 @@
         <v>22.5</v>
       </c>
       <c r="C49" t="n">
-        <v>26.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>24.4</v>
+        <v>62.5</v>
       </c>
       <c r="E49" t="n">
         <v>28.2</v>
@@ -31286,10 +31286,10 @@
         <v>33</v>
       </c>
       <c r="T49" t="n">
-        <v>15.4</v>
+        <v>70.8</v>
       </c>
       <c r="U49" t="n">
-        <v>19.5</v>
+        <v>50.5</v>
       </c>
       <c r="V49" t="n">
         <v>25.5</v>
@@ -31298,7 +31298,7 @@
         <v>25.2</v>
       </c>
       <c r="X49" t="n">
-        <v>26</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Y49" t="n">
         <v>27.4</v>
@@ -31316,13 +31316,13 @@
         <v>31.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>13.8</v>
+        <v>49.2</v>
       </c>
       <c r="AE49" t="n">
         <v>24.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>18.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AG49" t="n">
         <v>26.1</v>
@@ -31331,7 +31331,7 @@
         <v>30.1</v>
       </c>
       <c r="AI49" t="n">
-        <v>18.4</v>
+        <v>58.7</v>
       </c>
       <c r="AJ49" t="n">
         <v>24.2</v>
@@ -31343,7 +31343,7 @@
         <v>33.3</v>
       </c>
       <c r="AM49" t="n">
-        <v>22</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AN49" t="n">
         <v>18.4</v>
@@ -31355,7 +31355,7 @@
         <v>23.2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>17.5</v>
+        <v>57.4</v>
       </c>
       <c r="AR49" t="n">
         <v>27.6</v>
@@ -31367,7 +31367,7 @@
         <v>31.5</v>
       </c>
       <c r="AU49" t="n">
-        <v>18</v>
+        <v>49.9</v>
       </c>
       <c r="AV49" t="n">
         <v>22.7</v>
@@ -31376,7 +31376,7 @@
         <v>23.8</v>
       </c>
       <c r="AX49" t="n">
-        <v>14.7</v>
+        <v>67.5</v>
       </c>
       <c r="AY49" t="n">
         <v>24</v>
@@ -31400,10 +31400,10 @@
         <v>30.5</v>
       </c>
       <c r="BF49" t="n">
-        <v>15.3</v>
+        <v>50.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>18.2</v>
+        <v>47.5</v>
       </c>
       <c r="BH49" t="n">
         <v>23.7</v>
@@ -31412,7 +31412,7 @@
         <v>30.9</v>
       </c>
       <c r="BJ49" t="n">
-        <v>17.2</v>
+        <v>60.7</v>
       </c>
       <c r="BK49" t="n">
         <v>28.3</v>
@@ -31424,7 +31424,7 @@
         <v>26.3</v>
       </c>
       <c r="BN49" t="n">
-        <v>20.2</v>
+        <v>65.5</v>
       </c>
       <c r="BO49" t="n">
         <v>24.3</v>
@@ -31433,10 +31433,10 @@
         <v>22.6</v>
       </c>
       <c r="BQ49" t="n">
-        <v>22.5</v>
+        <v>58.4</v>
       </c>
       <c r="BR49" t="n">
-        <v>21.6</v>
+        <v>72.8</v>
       </c>
       <c r="BS49" t="n">
         <v>27.5</v>
@@ -31445,10 +31445,10 @@
         <v>25.1</v>
       </c>
       <c r="BU49" t="n">
-        <v>23.3</v>
+        <v>53.7</v>
       </c>
       <c r="BV49" t="n">
-        <v>18.9</v>
+        <v>68.7</v>
       </c>
       <c r="BW49" t="n">
         <v>27.3</v>
@@ -31460,7 +31460,7 @@
         <v>31.5</v>
       </c>
       <c r="BZ49" t="n">
-        <v>21.9</v>
+        <v>55.3</v>
       </c>
       <c r="CA49" t="n">
         <v>25.1</v>
@@ -31469,13 +31469,13 @@
         <v>28.3</v>
       </c>
       <c r="CC49" t="n">
-        <v>23.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="CD49" t="n">
         <v>25.2</v>
       </c>
       <c r="CE49" t="n">
-        <v>19.6</v>
+        <v>68.3</v>
       </c>
       <c r="CF49" t="n">
         <v>25.2</v>
@@ -31484,13 +31484,13 @@
         <v>34.1</v>
       </c>
       <c r="CH49" t="n">
-        <v>21.7</v>
+        <v>63</v>
       </c>
       <c r="CI49" t="n">
         <v>29</v>
       </c>
       <c r="CJ49" t="n">
-        <v>22.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="CK49" t="n">
         <v>24.2</v>
@@ -31505,7 +31505,7 @@
         <v>20.2</v>
       </c>
       <c r="CO49" t="n">
-        <v>17.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="CP49" t="n">
         <v>29.7</v>
@@ -31529,7 +31529,7 @@
         <v>29.8</v>
       </c>
       <c r="CW49" t="n">
-        <v>15.2</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="50">
@@ -31542,10 +31542,10 @@
         <v>21.2</v>
       </c>
       <c r="C50" t="n">
-        <v>11.5</v>
+        <v>54.5</v>
       </c>
       <c r="D50" t="n">
-        <v>23</v>
+        <v>54.6</v>
       </c>
       <c r="E50" t="n">
         <v>20.7</v>
@@ -31566,10 +31566,10 @@
         <v>18.2</v>
       </c>
       <c r="K50" t="n">
-        <v>17.3</v>
+        <v>40.4</v>
       </c>
       <c r="L50" t="n">
-        <v>19.2</v>
+        <v>62.4</v>
       </c>
       <c r="M50" t="n">
         <v>16.9</v>
@@ -31593,19 +31593,19 @@
         <v>28.2</v>
       </c>
       <c r="T50" t="n">
-        <v>17.5</v>
+        <v>66.7</v>
       </c>
       <c r="U50" t="n">
         <v>24.2</v>
       </c>
       <c r="V50" t="n">
-        <v>16.1</v>
+        <v>56.3</v>
       </c>
       <c r="W50" t="n">
         <v>21.9</v>
       </c>
       <c r="X50" t="n">
-        <v>16.3</v>
+        <v>57.7</v>
       </c>
       <c r="Y50" t="n">
         <v>29.2</v>
@@ -31629,7 +31629,7 @@
         <v>19.3</v>
       </c>
       <c r="AF50" t="n">
-        <v>4.6</v>
+        <v>42.9</v>
       </c>
       <c r="AG50" t="n">
         <v>22.7</v>
@@ -31638,25 +31638,25 @@
         <v>21.2</v>
       </c>
       <c r="AI50" t="n">
-        <v>18.2</v>
+        <v>57.6</v>
       </c>
       <c r="AJ50" t="n">
-        <v>15.5</v>
+        <v>43.6</v>
       </c>
       <c r="AK50" t="n">
         <v>22.5</v>
       </c>
       <c r="AL50" t="n">
-        <v>14.9</v>
+        <v>42.4</v>
       </c>
       <c r="AM50" t="n">
         <v>24.6</v>
       </c>
       <c r="AN50" t="n">
-        <v>15.4</v>
+        <v>47</v>
       </c>
       <c r="AO50" t="n">
-        <v>16.3</v>
+        <v>60.3</v>
       </c>
       <c r="AP50" t="n">
         <v>25</v>
@@ -31668,10 +31668,10 @@
         <v>29.4</v>
       </c>
       <c r="AS50" t="n">
-        <v>19.1</v>
+        <v>62.4</v>
       </c>
       <c r="AT50" t="n">
-        <v>16.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AU50" t="n">
         <v>16.3</v>
@@ -31698,7 +31698,7 @@
         <v>25.4</v>
       </c>
       <c r="BC50" t="n">
-        <v>16.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="BD50" t="n">
         <v>19.4</v>
@@ -31707,7 +31707,7 @@
         <v>19.4</v>
       </c>
       <c r="BF50" t="n">
-        <v>19.9</v>
+        <v>49.5</v>
       </c>
       <c r="BG50" t="n">
         <v>21.3</v>
@@ -31719,19 +31719,19 @@
         <v>20</v>
       </c>
       <c r="BJ50" t="n">
-        <v>15.1</v>
+        <v>50.6</v>
       </c>
       <c r="BK50" t="n">
         <v>28.5</v>
       </c>
       <c r="BL50" t="n">
-        <v>18.2</v>
+        <v>50.4</v>
       </c>
       <c r="BM50" t="n">
         <v>25.5</v>
       </c>
       <c r="BN50" t="n">
-        <v>17.9</v>
+        <v>56.5</v>
       </c>
       <c r="BO50" t="n">
         <v>20.8</v>
@@ -31743,19 +31743,19 @@
         <v>19.4</v>
       </c>
       <c r="BR50" t="n">
-        <v>17.1</v>
+        <v>60.7</v>
       </c>
       <c r="BS50" t="n">
-        <v>18.5</v>
+        <v>56.4</v>
       </c>
       <c r="BT50" t="n">
-        <v>14.1</v>
+        <v>43.5</v>
       </c>
       <c r="BU50" t="n">
-        <v>17.8</v>
+        <v>56</v>
       </c>
       <c r="BV50" t="n">
-        <v>19.4</v>
+        <v>51.2</v>
       </c>
       <c r="BW50" t="n">
         <v>18.8</v>
@@ -31767,7 +31767,7 @@
         <v>28.6</v>
       </c>
       <c r="BZ50" t="n">
-        <v>16.9</v>
+        <v>51.4</v>
       </c>
       <c r="CA50" t="n">
         <v>20.3</v>
@@ -31800,13 +31800,13 @@
         <v>23.6</v>
       </c>
       <c r="CK50" t="n">
-        <v>15.5</v>
+        <v>64</v>
       </c>
       <c r="CL50" t="n">
-        <v>19.1</v>
+        <v>54.8</v>
       </c>
       <c r="CM50" t="n">
-        <v>16.9</v>
+        <v>57.7</v>
       </c>
       <c r="CN50" t="n">
         <v>21.7</v>
@@ -31818,10 +31818,10 @@
         <v>21.7</v>
       </c>
       <c r="CQ50" t="n">
-        <v>14.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="CR50" t="n">
-        <v>11.3</v>
+        <v>46.5</v>
       </c>
       <c r="CS50" t="n">
         <v>18.1</v>
@@ -31846,7 +31846,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>14.4</v>
+        <v>60</v>
       </c>
       <c r="C51" t="n">
         <v>23.1</v>
@@ -31861,7 +31861,7 @@
         <v>24.2</v>
       </c>
       <c r="G51" t="n">
-        <v>23.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H51" t="n">
         <v>22.3</v>
@@ -31891,7 +31891,7 @@
         <v>34.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>17.7</v>
+        <v>60.6</v>
       </c>
       <c r="R51" t="n">
         <v>27.3</v>
@@ -31915,7 +31915,7 @@
         <v>25.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>13.8</v>
+        <v>50.2</v>
       </c>
       <c r="Z51" t="n">
         <v>31.7</v>
@@ -31963,7 +31963,7 @@
         <v>38</v>
       </c>
       <c r="AO51" t="n">
-        <v>20</v>
+        <v>50.2</v>
       </c>
       <c r="AP51" t="n">
         <v>27.4</v>
@@ -31972,7 +31972,7 @@
         <v>21.6</v>
       </c>
       <c r="AR51" t="n">
-        <v>19.4</v>
+        <v>54.4</v>
       </c>
       <c r="AS51" t="n">
         <v>19.6</v>
@@ -31999,22 +31999,22 @@
         <v>21.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>16.2</v>
+        <v>47.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>13.6</v>
+        <v>58.2</v>
       </c>
       <c r="BC51" t="n">
-        <v>18.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BD51" t="n">
-        <v>21.9</v>
+        <v>54.5</v>
       </c>
       <c r="BE51" t="n">
         <v>25.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>19.6</v>
+        <v>61.5</v>
       </c>
       <c r="BG51" t="n">
         <v>22.1</v>
@@ -32053,7 +32053,7 @@
         <v>24.8</v>
       </c>
       <c r="BS51" t="n">
-        <v>18.1</v>
+        <v>51.6</v>
       </c>
       <c r="BT51" t="n">
         <v>29.4</v>
@@ -32101,10 +32101,10 @@
         <v>30</v>
       </c>
       <c r="CI51" t="n">
-        <v>19.5</v>
+        <v>59.8</v>
       </c>
       <c r="CJ51" t="n">
-        <v>19.9</v>
+        <v>61.7</v>
       </c>
       <c r="CK51" t="n">
         <v>33.1</v>
